--- a/Employee_Reports_wi52/Sugathadasa Pattiwilage Q0376.xlsx
+++ b/Employee_Reports_wi52/Sugathadasa Pattiwilage Q0376.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-517</v>
+        <v>-525</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-378</v>
+        <v>-386</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-378</v>
+        <v>-386</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1694,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1709,41 +1709,41 @@
       <c r="K26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H27" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
+      <c r="H27" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -1780,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -1829,11 +1829,11 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1866,11 +1866,11 @@
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -1915,11 +1915,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1952,11 +1952,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7907</v>
+        <v>7899</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7895</v>
+        <v>7887</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7895</v>
+        <v>7887</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
